--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.88179215622404</v>
+        <v>6.805791225386407</v>
       </c>
       <c r="D2" t="n">
-        <v>41.70794149579179</v>
+        <v>6.777540493066166</v>
       </c>
       <c r="E2" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F2" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.21653135458521</v>
+        <v>6.210186345120096</v>
       </c>
       <c r="D3" t="n">
-        <v>37.99935585551731</v>
+        <v>6.174895326521563</v>
       </c>
       <c r="E3" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F3" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.86918733757036</v>
+        <v>5.016242942355183</v>
       </c>
       <c r="D4" t="n">
-        <v>30.64125127012145</v>
+        <v>4.979203331394737</v>
       </c>
       <c r="E4" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F4" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.7781864996181</v>
+        <v>4.513955306187941</v>
       </c>
       <c r="D5" t="n">
-        <v>27.57738899563174</v>
+        <v>4.481325711790157</v>
       </c>
       <c r="E5" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F5" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.25739480401297</v>
+        <v>5.241826655652108</v>
       </c>
       <c r="D6" t="n">
-        <v>32.11969604115564</v>
+        <v>5.219450606687792</v>
       </c>
       <c r="E6" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F6" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.79430229085489</v>
+        <v>6.466574122263919</v>
       </c>
       <c r="D7" t="n">
-        <v>39.71435133464761</v>
+        <v>6.453582091880237</v>
       </c>
       <c r="E7" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F7" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.7423674223471</v>
+        <v>4.508134706131403</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70316146039523</v>
+        <v>4.501763737314224</v>
       </c>
       <c r="E8" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F8" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.62158133129731</v>
+        <v>5.463506966335813</v>
       </c>
       <c r="D9" t="n">
-        <v>33.67420605334898</v>
+        <v>5.47205848366921</v>
       </c>
       <c r="E9" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F9" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.27905807391811</v>
+        <v>1.507846937011693</v>
       </c>
       <c r="D10" t="n">
-        <v>9.440050449605069</v>
+        <v>1.534008198060824</v>
       </c>
       <c r="E10" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F10" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.40482119574812</v>
+        <v>2.828283444309069</v>
       </c>
       <c r="D11" t="n">
-        <v>17.57104038244779</v>
+        <v>2.855294062147765</v>
       </c>
       <c r="E11" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F11" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.89334268708254</v>
+        <v>4.857668186650914</v>
       </c>
       <c r="D12" t="n">
-        <v>30.05555923360107</v>
+        <v>4.884028375460174</v>
       </c>
       <c r="E12" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F12" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.8901586215287</v>
+        <v>6.644650775998413</v>
       </c>
       <c r="D13" t="n">
-        <v>41.04274995142779</v>
+        <v>6.669446867107017</v>
       </c>
       <c r="E13" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F13" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.21328377541384</v>
+        <v>6.37215861350475</v>
       </c>
       <c r="D14" t="n">
-        <v>39.36243434055616</v>
+        <v>6.396395580340377</v>
       </c>
       <c r="E14" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F14" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.47078419055198</v>
+        <v>5.764002430964697</v>
       </c>
       <c r="D15" t="n">
-        <v>35.69788129844566</v>
+        <v>5.800905710997419</v>
       </c>
       <c r="E15" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F15" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.78039622523092</v>
+        <v>6.464314386600026</v>
       </c>
       <c r="D16" t="n">
-        <v>39.99112392209476</v>
+        <v>6.4985576373404</v>
       </c>
       <c r="E16" t="n">
-        <v>8.843832816372878</v>
+        <v>1.437122832660593</v>
       </c>
       <c r="F16" t="n">
-        <v>8.815282141911116</v>
+        <v>1.432483348060556</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
